--- a/artfynd/A 59219-2022 artfynd.xlsx
+++ b/artfynd/A 59219-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59219-2022 artfynd.xlsx
+++ b/artfynd/A 59219-2022 artfynd.xlsx
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69885332</v>
+        <v>112182731</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lycksaberg, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636471.0755041959</v>
+        <v>636506</v>
       </c>
       <c r="R2" t="n">
-        <v>7215624.137678899</v>
+        <v>7215899</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109808070</v>
+        <v>109808029</v>
       </c>
       <c r="B3" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636289.417431826</v>
+        <v>636366</v>
       </c>
       <c r="R3" t="n">
-        <v>7215946.207034735</v>
+        <v>7215953</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +861,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109808043</v>
+        <v>109808072</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636457.9246487151</v>
+        <v>636289</v>
       </c>
       <c r="R4" t="n">
-        <v>7215744.531195947</v>
+        <v>7215945</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +958,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +968,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109808050</v>
+        <v>109808058</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636384.4667793319</v>
+        <v>636250</v>
       </c>
       <c r="R5" t="n">
-        <v>7215711.545997364</v>
+        <v>7215791</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,6 +1084,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109808038</v>
+        <v>109808043</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636537.0814717311</v>
+        <v>636458</v>
       </c>
       <c r="R6" t="n">
-        <v>7215653.39901273</v>
+        <v>7215744</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109808067</v>
+        <v>109808049</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636289.9044700463</v>
+        <v>636403</v>
       </c>
       <c r="R7" t="n">
-        <v>7215926.347002966</v>
+        <v>7215744</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109808039</v>
+        <v>109808059</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636525.5640889079</v>
+        <v>636273</v>
       </c>
       <c r="R8" t="n">
-        <v>7215627.485617347</v>
+        <v>7215792</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109808058</v>
+        <v>109808063</v>
       </c>
       <c r="B9" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636250.3725512157</v>
+        <v>636287</v>
       </c>
       <c r="R9" t="n">
-        <v>7215790.854258896</v>
+        <v>7215833</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,7 +1513,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1577,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109808041</v>
+        <v>109808069</v>
       </c>
       <c r="B10" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636514.8575524407</v>
+        <v>636280</v>
       </c>
       <c r="R10" t="n">
-        <v>7215685.377867224</v>
+        <v>7215931</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1652,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,37 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109808042</v>
+        <v>109808068</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636511.8444164334</v>
+        <v>636280</v>
       </c>
       <c r="R11" t="n">
-        <v>7215677.201207426</v>
+        <v>7215931</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1764,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109808029</v>
+        <v>109808040</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636366.1648209152</v>
+        <v>636514</v>
       </c>
       <c r="R12" t="n">
-        <v>7215953.534125699</v>
+        <v>7215684</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1876,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109808034</v>
+        <v>109808046</v>
       </c>
       <c r="B13" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636604.9327490077</v>
+        <v>636457</v>
       </c>
       <c r="R13" t="n">
-        <v>7215808.395404725</v>
+        <v>7215730</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1988,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,15 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109808061</v>
+        <v>109808062</v>
       </c>
       <c r="B14" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636287.7259172894</v>
+        <v>636287</v>
       </c>
       <c r="R14" t="n">
-        <v>7215835.294206594</v>
+        <v>7215833</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2140,12 +2069,7 @@
         <v>109808064</v>
       </c>
       <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636262.1318413562</v>
+        <v>636262</v>
       </c>
       <c r="R15" t="n">
-        <v>7215903.922188178</v>
+        <v>7215904</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109808037</v>
+        <v>109808041</v>
       </c>
       <c r="B16" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636546.1363682537</v>
+        <v>636515</v>
       </c>
       <c r="R16" t="n">
-        <v>7215640.699616516</v>
+        <v>7215685</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2324,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109808036</v>
+        <v>69885331</v>
       </c>
       <c r="B17" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,37 +2291,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lycksaliden, Ly lm</t>
+          <t>Strömnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636545.3879416399</v>
+        <v>636381</v>
       </c>
       <c r="R17" t="n">
-        <v>7215638.54986822</v>
+        <v>7215962</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,22 +2345,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2017-08-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2017-08-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,27 +2370,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109808069</v>
+        <v>69885332</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,37 +2393,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lycksaliden, Ly lm</t>
+          <t>Lycksaberg, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636279.5092815987</v>
+        <v>636471</v>
       </c>
       <c r="R18" t="n">
-        <v>7215931.369795786</v>
+        <v>7215624</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2543,22 +2447,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>06:43</t>
+          <t>2017-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>06:43</t>
+          <t>2017-08-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,27 +2472,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109808057</v>
+        <v>109808050</v>
       </c>
       <c r="B19" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,43 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636327.5112064613</v>
+        <v>636384</v>
       </c>
       <c r="R19" t="n">
-        <v>7215789.737261463</v>
+        <v>7215712</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,15 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109808049</v>
+        <v>109808060</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636402.8993033766</v>
+        <v>636294</v>
       </c>
       <c r="R20" t="n">
-        <v>7215743.698131301</v>
+        <v>7215816</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,37 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109808056</v>
+        <v>109808039</v>
       </c>
       <c r="B21" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2858,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636230.4713720218</v>
+        <v>636525</v>
       </c>
       <c r="R21" t="n">
-        <v>7215781.481193361</v>
+        <v>7215627</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,37 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109808040</v>
+        <v>109808042</v>
       </c>
       <c r="B22" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636513.6282727523</v>
+        <v>636512</v>
       </c>
       <c r="R22" t="n">
-        <v>7215684.475282712</v>
+        <v>7215677</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,37 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109808031</v>
+        <v>109808030</v>
       </c>
       <c r="B23" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636581.6892440468</v>
+        <v>636369</v>
       </c>
       <c r="R23" t="n">
-        <v>7215844.132628254</v>
+        <v>7215953</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,37 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109808062</v>
+        <v>109808070</v>
       </c>
       <c r="B24" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636286.9580101221</v>
+        <v>636289</v>
       </c>
       <c r="R24" t="n">
-        <v>7215833.566827052</v>
+        <v>7215946</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3229,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:57</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,50 +3126,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109808032</v>
+        <v>109808048</v>
       </c>
       <c r="B25" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636601.2216289758</v>
+        <v>636415</v>
       </c>
       <c r="R25" t="n">
-        <v>7215815.416737095</v>
+        <v>7215748</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3341,7 +3201,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3211,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,50 +3238,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109808063</v>
+        <v>109808598</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636286.9580101221</v>
+        <v>636380</v>
       </c>
       <c r="R26" t="n">
-        <v>7215833.566827052</v>
+        <v>7216117</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,22 +3312,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,15 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109808054</v>
+        <v>109808057</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,34 +3365,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636267.2396241958</v>
+        <v>636328</v>
       </c>
       <c r="R27" t="n">
-        <v>7215737.053556271</v>
+        <v>7215790</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3565,7 +3433,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3443,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,15 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109808072</v>
+        <v>109808055</v>
       </c>
       <c r="B28" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,34 +3481,48 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636289.4561418504</v>
+        <v>636233</v>
       </c>
       <c r="R28" t="n">
-        <v>7215945.362754301</v>
+        <v>7215750</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3677,7 +3554,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3564,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,12 +3594,7 @@
         <v>109808045</v>
       </c>
       <c r="B29" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3754,10 +3626,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636454.3761246675</v>
+        <v>636454</v>
       </c>
       <c r="R29" t="n">
-        <v>7215729.561228487</v>
+        <v>7215730</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3826,15 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109808046</v>
+        <v>109808061</v>
       </c>
       <c r="B30" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,21 +3709,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3866,10 +3733,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636457.2961124275</v>
+        <v>636288</v>
       </c>
       <c r="R30" t="n">
-        <v>7215730.541381726</v>
+        <v>7215835</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3901,7 +3768,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3778,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>06:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,37 +3805,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109808033</v>
+        <v>109808066</v>
       </c>
       <c r="B31" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>6000248</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636601.2216289758</v>
+        <v>636291</v>
       </c>
       <c r="R31" t="n">
-        <v>7215815.416737095</v>
+        <v>7215925</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4013,7 +3875,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +3885,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4050,37 +3912,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109808060</v>
+        <v>109808031</v>
       </c>
       <c r="B32" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4090,10 +3947,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636294.091525406</v>
+        <v>636582</v>
       </c>
       <c r="R32" t="n">
-        <v>7215816.549050149</v>
+        <v>7215844</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4125,7 +3982,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,7 +3992,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,37 +4019,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109808066</v>
+        <v>109808032</v>
       </c>
       <c r="B33" t="n">
-        <v>76489</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6000248</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4054,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636290.788479645</v>
+        <v>636601</v>
       </c>
       <c r="R33" t="n">
-        <v>7215925.541473595</v>
+        <v>7215815</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4237,7 +4089,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4247,7 +4099,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,15 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109808048</v>
+        <v>109808034</v>
       </c>
       <c r="B34" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4290,39 +4137,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636414.9825464042</v>
+        <v>636605</v>
       </c>
       <c r="R34" t="n">
-        <v>7215748.060103338</v>
+        <v>7215809</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4354,7 +4196,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4206,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,15 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109808059</v>
+        <v>109808037</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4407,21 +4244,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4431,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636273.5999816291</v>
+        <v>636546</v>
       </c>
       <c r="R35" t="n">
-        <v>7215792.341997568</v>
+        <v>7215641</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4466,7 +4303,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:04</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4313,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:04</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,15 +4340,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109808068</v>
+        <v>109808038</v>
       </c>
       <c r="B36" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4519,21 +4351,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4543,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636279.5092815987</v>
+        <v>636537</v>
       </c>
       <c r="R36" t="n">
-        <v>7215931.369795786</v>
+        <v>7215654</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4578,7 +4410,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4420,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,15 +4447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109808053</v>
+        <v>109808033</v>
       </c>
       <c r="B37" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4631,21 +4458,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4655,10 +4482,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636318.4286170915</v>
+        <v>636601</v>
       </c>
       <c r="R37" t="n">
-        <v>7215719.93972162</v>
+        <v>7215815</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4690,7 +4517,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4527,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4727,57 +4554,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112182731</v>
+        <v>109808036</v>
       </c>
       <c r="B38" t="n">
-        <v>90152</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lycksaberg, Ly lm</t>
+          <t>Lycksaliden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636506</v>
+        <v>636545</v>
       </c>
       <c r="R38" t="n">
-        <v>7215899</v>
+        <v>7215639</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4801,17 +4619,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,12 +4649,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
